--- a/templates/Trackr-positions-template.xlsx
+++ b/templates/Trackr-positions-template.xlsx
@@ -551,7 +551,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>• Quantity — Number of shares / units held at this broker (decimals allowed).</v>
+        <v>• Quantity — Number of shares / units held at this broker (decimals allowed). If unknown, give Value and Current Price instead.</v>
       </c>
     </row>
     <row r="16">
@@ -561,7 +561,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>• Invested — Optional — total amount invested in this position. Used when Avg Buy Price is empty.</v>
+        <v>• Invested — Total amount invested in this position (your exact cost basis). If the app shows Value and gain, Invested = Value − gain. Preferred over Avg Buy Price when both are given.</v>
       </c>
     </row>
     <row r="18">
